--- a/Team-Data/2014-15/2-11-2014-15.xlsx
+++ b/Team-Data/2014-15/2-11-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
         <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.796</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J2" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L2" t="n">
         <v>9.9</v>
       </c>
       <c r="M2" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.389</v>
+        <v>0.393</v>
       </c>
       <c r="O2" t="n">
         <v>17.5</v>
@@ -700,25 +767,25 @@
         <v>22.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S2" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="V2" t="n">
         <v>14</v>
       </c>
       <c r="W2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
@@ -727,19 +794,19 @@
         <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.4</v>
+        <v>103.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>10</v>
@@ -760,7 +827,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -772,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
         <v>17</v>
@@ -784,7 +851,7 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
@@ -796,7 +863,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>16</v>
@@ -805,7 +872,7 @@
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -843,61 +910,61 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
         <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>0.392</v>
+        <v>0.38</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="J3" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L3" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M3" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="N3" t="n">
         <v>0.327</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P3" t="n">
         <v>19.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.755</v>
+        <v>0.751</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="U3" t="n">
         <v>24.5</v>
       </c>
       <c r="V3" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W3" t="n">
         <v>8</v>
@@ -909,13 +976,13 @@
         <v>5.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
         <v>-1.5</v>
@@ -924,31 +991,31 @@
         <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>14</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>13</v>
       </c>
       <c r="AM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN3" t="n">
         <v>24</v>
@@ -960,22 +1027,22 @@
         <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -987,7 +1054,7 @@
         <v>23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1115,7 +1182,7 @@
         <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>23</v>
@@ -1124,7 +1191,7 @@
         <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>25</v>
@@ -1136,13 +1203,13 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1172,7 +1239,7 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1324,10 +1391,10 @@
         <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
         <v>5</v>
@@ -1348,13 +1415,13 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1530,10 +1597,10 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA6" t="n">
         <v>3</v>
@@ -1542,7 +1609,7 @@
         <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -1571,43 +1638,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.611</v>
+        <v>0.604</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>25.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0.753</v>
@@ -1622,7 +1689,7 @@
         <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
         <v>13.9</v>
@@ -1631,7 +1698,7 @@
         <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y7" t="n">
         <v>4.8</v>
@@ -1643,34 +1710,34 @@
         <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.2</v>
+        <v>102</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1685,16 +1752,16 @@
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
@@ -1703,7 +1770,7 @@
         <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1712,7 +1779,7 @@
         <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1724,7 +1791,7 @@
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -1756,40 +1823,40 @@
         <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.648</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="J8" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N8" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O8" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
         <v>0.756</v>
@@ -1798,16 +1865,16 @@
         <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
         <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W8" t="n">
         <v>8.1</v>
@@ -1825,16 +1892,16 @@
         <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.5</v>
+        <v>106.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
         <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>7</v>
@@ -1843,28 +1910,28 @@
         <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL8" t="n">
         <v>6</v>
       </c>
-      <c r="AL8" t="n">
-        <v>5</v>
-      </c>
       <c r="AM8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
@@ -1873,13 +1940,13 @@
         <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1894,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
@@ -1903,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -2013,34 +2080,34 @@
         <v>-3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="n">
         <v>22</v>
       </c>
-      <c r="AF9" t="n">
-        <v>21</v>
-      </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN9" t="n">
         <v>28</v>
@@ -2049,13 +2116,13 @@
         <v>7</v>
       </c>
       <c r="AP9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR9" t="n">
         <v>5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2064,13 +2131,13 @@
         <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2082,10 +2149,10 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -2117,64 +2184,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
         <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.389</v>
+        <v>0.396</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.428</v>
+        <v>0.429</v>
       </c>
       <c r="L10" t="n">
         <v>8.6</v>
       </c>
       <c r="M10" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O10" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0.712</v>
       </c>
       <c r="R10" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S10" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T10" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="U10" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V10" t="n">
         <v>13.7</v>
       </c>
       <c r="W10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X10" t="n">
         <v>4.5</v>
@@ -2183,19 +2250,19 @@
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>19</v>
@@ -2204,7 +2271,7 @@
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
@@ -2240,28 +2307,28 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
         <v>17</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
         <v>21</v>
@@ -2270,7 +2337,7 @@
         <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.824</v>
+        <v>0.82</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,25 +2384,25 @@
         <v>41.8</v>
       </c>
       <c r="J11" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.481</v>
       </c>
       <c r="L11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M11" t="n">
         <v>27.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.384</v>
+        <v>0.387</v>
       </c>
       <c r="O11" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P11" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0.774</v>
@@ -2344,13 +2411,13 @@
         <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="T11" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="U11" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="V11" t="n">
         <v>14.9</v>
@@ -2362,19 +2429,19 @@
         <v>6.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z11" t="n">
         <v>19.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>110.6</v>
+        <v>110.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="AD11" t="n">
         <v>29</v>
@@ -2404,13 +2471,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN11" t="n">
         <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP11" t="n">
         <v>23</v>
@@ -2419,7 +2486,7 @@
         <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2440,7 +2507,7 @@
         <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -2484,13 +2551,13 @@
         <v>52</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.673</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,7 +2566,7 @@
         <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="K12" t="n">
         <v>0.44</v>
@@ -2508,31 +2575,31 @@
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.349</v>
+        <v>0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
         <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V12" t="n">
         <v>16.9</v>
@@ -2550,34 +2617,34 @@
         <v>22.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,28 +2656,28 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
         <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,7 +2686,7 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>0.389</v>
+        <v>0.377</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J13" t="n">
-        <v>83.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
@@ -2693,76 +2760,76 @@
         <v>20.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O13" t="n">
         <v>16.3</v>
       </c>
       <c r="P13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.764</v>
+        <v>0.761</v>
       </c>
       <c r="R13" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S13" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T13" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>14.4</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y13" t="n">
         <v>4.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA13" t="n">
         <v>20.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
@@ -2777,13 +2844,13 @@
         <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
         <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2795,28 +2862,28 @@
         <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14" t="n">
         <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0.648</v>
+        <v>0.642</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2869,67 +2936,67 @@
         <v>0.472</v>
       </c>
       <c r="L14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P14" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.738</v>
+        <v>0.742</v>
       </c>
       <c r="R14" t="n">
         <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V14" t="n">
         <v>11.9</v>
       </c>
       <c r="W14" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X14" t="n">
         <v>4.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AB14" t="n">
         <v>106.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF14" t="n">
         <v>7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>8</v>
       </c>
       <c r="AG14" t="n">
         <v>8</v>
@@ -2938,16 +3005,16 @@
         <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>19</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM14" t="n">
         <v>6</v>
@@ -2956,13 +3023,13 @@
         <v>5</v>
       </c>
       <c r="AO14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP14" t="n">
         <v>5</v>
       </c>
-      <c r="AP14" t="n">
-        <v>4</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -2992,10 +3059,10 @@
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -3042,10 +3109,10 @@
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86</v>
       </c>
       <c r="K15" t="n">
         <v>0.433</v>
@@ -3054,28 +3121,28 @@
         <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="U15" t="n">
         <v>20.7</v>
@@ -3084,19 +3151,19 @@
         <v>13.1</v>
       </c>
       <c r="W15" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="n">
         <v>99.3</v>
@@ -3105,13 +3172,13 @@
         <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3120,10 +3187,10 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>27</v>
@@ -3138,43 +3205,43 @@
         <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>21</v>
       </c>
       <c r="AV15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -3209,70 +3276,70 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.736</v>
+        <v>0.75</v>
       </c>
       <c r="H16" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I16" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J16" t="n">
         <v>83.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O16" t="n">
         <v>18.5</v>
       </c>
       <c r="P16" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R16" t="n">
         <v>10.6</v>
       </c>
       <c r="S16" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T16" t="n">
         <v>43.2</v>
       </c>
       <c r="U16" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="V16" t="n">
         <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z16" t="n">
         <v>19.2</v>
@@ -3281,13 +3348,13 @@
         <v>20.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.6</v>
+        <v>100.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,31 +3366,31 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK16" t="n">
         <v>7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
       </c>
       <c r="AM16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
         <v>5</v>
@@ -3332,13 +3399,13 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT16" t="n">
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
         <v>5</v>
@@ -3347,7 +3414,7 @@
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
@@ -3356,13 +3423,13 @@
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
         <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.423</v>
+        <v>0.431</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
@@ -3409,37 +3476,37 @@
         <v>34.3</v>
       </c>
       <c r="J17" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O17" t="n">
         <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="U17" t="n">
         <v>20.1</v>
@@ -3448,28 +3515,28 @@
         <v>14.6</v>
       </c>
       <c r="W17" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X17" t="n">
         <v>4.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z17" t="n">
         <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
         <v>92.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>20</v>
@@ -3508,7 +3575,7 @@
         <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3532,7 +3599,7 @@
         <v>24</v>
       </c>
       <c r="AY17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
         <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3600,34 +3667,34 @@
         <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R18" t="n">
         <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
         <v>23.7</v>
       </c>
       <c r="V18" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W18" t="n">
         <v>9.6</v>
@@ -3642,16 +3709,16 @@
         <v>22.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3663,16 +3730,16 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL18" t="n">
         <v>19</v>
@@ -3681,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="AN18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO18" t="n">
         <v>26</v>
@@ -3690,10 +3757,10 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
         <v>24</v>
@@ -3714,13 +3781,13 @@
         <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
         <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
         <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>0.208</v>
+        <v>0.212</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J19" t="n">
         <v>84.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
         <v>5.1</v>
@@ -3785,25 +3852,25 @@
         <v>14.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O19" t="n">
         <v>18.8</v>
       </c>
       <c r="P19" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0.758</v>
       </c>
       <c r="R19" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T19" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
         <v>22.1</v>
@@ -3821,40 +3888,40 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA19" t="n">
         <v>21.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.5</v>
+        <v>97.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
       </c>
       <c r="AF19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG19" t="n">
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="n">
         <v>11</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3875,7 +3942,7 @@
         <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3884,7 +3951,7 @@
         <v>26</v>
       </c>
       <c r="AU19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV19" t="n">
         <v>26</v>
@@ -3893,7 +3960,7 @@
         <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -3940,25 +4007,25 @@
         <v>52</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J20" t="n">
-        <v>83.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
         <v>6.8</v>
@@ -3967,40 +4034,40 @@
         <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.356</v>
+        <v>0.353</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="S20" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T20" t="n">
-        <v>43.7</v>
+        <v>44.3</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
         <v>18.8</v>
@@ -4009,43 +4076,43 @@
         <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>12</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AK20" t="n">
         <v>14</v>
       </c>
-      <c r="AK20" t="n">
-        <v>13</v>
-      </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
@@ -4054,28 +4121,28 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>30</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -4119,49 +4186,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.436</v>
+        <v>0.438</v>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N21" t="n">
         <v>0.359</v>
       </c>
       <c r="O21" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="P21" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="Q21" t="n">
         <v>0.769</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
         <v>29.1</v>
@@ -4170,10 +4237,10 @@
         <v>39.8</v>
       </c>
       <c r="U21" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
         <v>7.2</v>
@@ -4188,16 +4255,16 @@
         <v>21.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.7</v>
+        <v>-7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4212,22 +4279,22 @@
         <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM21" t="n">
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4248,10 +4315,10 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" t="n">
         <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>0.528</v>
+        <v>0.519</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,7 +4386,7 @@
         <v>37.7</v>
       </c>
       <c r="J22" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.444</v>
@@ -4328,28 +4395,28 @@
         <v>7.4</v>
       </c>
       <c r="M22" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N22" t="n">
         <v>0.325</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P22" t="n">
         <v>23.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="R22" t="n">
         <v>11.9</v>
       </c>
       <c r="S22" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="T22" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="U22" t="n">
         <v>20.3</v>
@@ -4361,7 +4428,7 @@
         <v>7.2</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
         <v>4.5</v>
@@ -4373,13 +4440,13 @@
         <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
@@ -4391,7 +4458,7 @@
         <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>14</v>
@@ -4412,13 +4479,13 @@
         <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR22" t="n">
         <v>7</v>
@@ -4430,16 +4497,16 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV22" t="n">
         <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
@@ -4451,7 +4518,7 @@
         <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -4486,13 +4553,13 @@
         <v>55</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.309</v>
+        <v>0.291</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,10 +4568,10 @@
         <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
@@ -4516,22 +4583,22 @@
         <v>0.358</v>
       </c>
       <c r="O23" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="P23" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
         <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.5</v>
@@ -4546,19 +4613,19 @@
         <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA23" t="n">
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4576,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4591,7 +4658,7 @@
         <v>23</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>21</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4779,7 +4846,7 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4788,13 +4855,13 @@
         <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT24" t="n">
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
         <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4995,7 @@
         <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
         <v>14</v>
@@ -4937,7 +5004,7 @@
         <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
         <v>3</v>
@@ -4946,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>7</v>
@@ -4955,25 +5022,25 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ25" t="n">
         <v>2</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS25" t="n">
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
         <v>22</v>
@@ -4982,7 +5049,7 @@
         <v>22</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J26" t="n">
         <v>86.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L26" t="n">
         <v>10.1</v>
@@ -5062,28 +5129,28 @@
         <v>0.362</v>
       </c>
       <c r="O26" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P26" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.795</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="U26" t="n">
         <v>22.3</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
@@ -5095,37 +5162,37 @@
         <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
         <v>102.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5161,19 +5228,19 @@
         <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA26" t="n">
         <v>24</v>
@@ -5182,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" t="n">
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>0.346</v>
+        <v>0.353</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5229,7 +5296,7 @@
         <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="K27" t="n">
         <v>0.451</v>
@@ -5238,10 +5305,10 @@
         <v>5.1</v>
       </c>
       <c r="M27" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O27" t="n">
         <v>22.7</v>
@@ -5253,16 +5320,16 @@
         <v>0.773</v>
       </c>
       <c r="R27" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S27" t="n">
         <v>33.7</v>
       </c>
       <c r="T27" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U27" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V27" t="n">
         <v>16.4</v>
@@ -5286,16 +5353,16 @@
         <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.2</v>
+        <v>-4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5316,7 +5383,7 @@
         <v>29</v>
       </c>
       <c r="AM27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN27" t="n">
         <v>26</v>
@@ -5328,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
         <v>14</v>
@@ -5355,13 +5422,13 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -5408,52 +5475,52 @@
         <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J28" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
         <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
         <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W28" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5462,22 +5529,22 @@
         <v>19.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
@@ -5489,10 +5556,10 @@
         <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,25 +5568,25 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT28" t="n">
         <v>12</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5528,25 +5595,25 @@
         <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
         <v>14</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F29" t="n">
         <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J29" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
         <v>8.9</v>
@@ -5605,16 +5672,16 @@
         <v>25.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P29" t="n">
         <v>25.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.783</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
         <v>11.1</v>
@@ -5623,16 +5690,16 @@
         <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="n">
         <v>12.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X29" t="n">
         <v>4.5</v>
@@ -5641,31 +5708,31 @@
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>105.6</v>
+        <v>105.8</v>
       </c>
       <c r="AC29" t="n">
         <v>4.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5674,7 +5741,7 @@
         <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5683,7 +5750,7 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5698,7 +5765,7 @@
         <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT29" t="n">
         <v>22</v>
@@ -5713,22 +5780,22 @@
         <v>16</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -5757,61 +5824,61 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E30" t="n">
         <v>19</v>
       </c>
       <c r="F30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0.358</v>
+        <v>0.365</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J30" t="n">
         <v>79.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L30" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O30" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P30" t="n">
         <v>22.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.735</v>
+        <v>0.739</v>
       </c>
       <c r="R30" t="n">
         <v>11.8</v>
       </c>
       <c r="S30" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T30" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U30" t="n">
         <v>20.3</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
         <v>7</v>
@@ -5823,25 +5890,25 @@
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA30" t="n">
         <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.7</v>
+        <v>96</v>
       </c>
       <c r="AC30" t="n">
         <v>-2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
         <v>24</v>
@@ -5850,7 +5917,7 @@
         <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
@@ -5865,16 +5932,16 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5886,28 +5953,28 @@
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV30" t="n">
         <v>25</v>
       </c>
       <c r="AW30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA30" t="n">
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" t="n">
         <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0.611</v>
+        <v>0.623</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
@@ -5966,34 +6033,34 @@
         <v>6.1</v>
       </c>
       <c r="M31" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O31" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P31" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R31" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S31" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T31" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="U31" t="n">
         <v>24.4</v>
       </c>
       <c r="V31" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W31" t="n">
         <v>7.4</v>
@@ -6005,28 +6072,28 @@
         <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="AC31" t="n">
         <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
         <v>9</v>
       </c>
       <c r="AF31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH31" t="n">
         <v>11</v>
@@ -6035,7 +6102,7 @@
         <v>6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
         <v>4</v>
@@ -6047,40 +6114,40 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-11-2014-15</t>
+          <t>2015-02-11</t>
         </is>
       </c>
     </row>
